--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-humanname.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-humanname.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-humanname.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-humanname.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-humanname.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-humanname.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-humanname.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-humanname.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -376,7 +376,7 @@
 </t>
   </si>
   <si>
-    <t>通常|公式|一時的|ニックネーム|匿名|古い|未婚女性 / usual | official | temp | nickname | anonymous | old | maiden</t>
+    <t>通常|公式|一時的|ニックネーム|匿名|古い|旧姓 / usual | official | temp | nickname | anonymous | old | maiden</t>
   </si>
   <si>
     <t>この名前の目的を特定します。 / Identifies the purpose for this name.</t>
@@ -434,7 +434,7 @@
 </t>
   </si>
   <si>
-    <t>姓（「姓」と呼ばれることが多い） / Family name (often called 'Surname')</t>
+    <t>姓 / Family name (often called 'Surname')</t>
   </si>
   <si>
     <t>系図にリンクする名前の部分。一部の文化（例：エリトリア）では、息子の姓は父親の名です。 / The part of a name that links to the genealogy. In some cultures (e.g. Eritrea) the family name of a son is the first name of his father.</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-humanname.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-humanname.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-release</t>
+    <t>1.2.0-b</t>
   </si>
   <si>
     <t>Name</t>
